--- a/data/BenchmarkDatabaseCost.xlsx
+++ b/data/BenchmarkDatabaseCost.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\METALS-main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krishnan Suresh\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2252A4-AAE6-4451-A89A-E20F5C02DA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E51978-3266-4028-A38B-9D7040274C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>Material</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>Cost</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
 </sst>
 </file>
@@ -105,12 +108,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -166,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -199,6 +208,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -515,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -696,6 +717,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="13">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13">
+        <v>1240</v>
+      </c>
+      <c r="E5" s="13">
+        <v>1035</v>
+      </c>
+      <c r="F5" s="14">
+        <v>1E-3</v>
+      </c>
+      <c r="G5" s="13">
+        <v>7</v>
+      </c>
+      <c r="H5" s="13">
+        <v>1400</v>
+      </c>
+      <c r="I5" s="13">
+        <v>980</v>
+      </c>
+      <c r="J5" s="13">
+        <v>12</v>
+      </c>
+      <c r="K5" s="14">
+        <v>1E-10</v>
+      </c>
+      <c r="L5" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="M5" s="15">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/BenchmarkDatabaseCost.xlsx
+++ b/data/BenchmarkDatabaseCost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krishnan Suresh\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E51978-3266-4028-A38B-9D7040274C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F59DAC5-EE06-46D7-8344-76F72BB298B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,18 +108,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -175,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -208,18 +202,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -718,43 +700,43 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="4">
         <v>0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="4">
         <v>1240</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="4">
         <v>1035</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="11">
         <v>1E-3</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="4">
         <v>7</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="4">
         <v>1400</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="4">
         <v>980</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="4">
         <v>12</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="11">
         <v>1E-10</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="8">
         <v>0.87</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="8">
         <v>1</v>
       </c>
     </row>

--- a/data/BenchmarkDatabaseCost.xlsx
+++ b/data/BenchmarkDatabaseCost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krishnan Suresh\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E51978-3266-4028-A38B-9D7040274C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520BA14F-22C8-4326-93A7-3E7C1D6F5735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Material</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>Cost</t>
-  </si>
-  <si>
-    <t>D</t>
   </si>
 </sst>
 </file>
@@ -108,18 +105,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -175,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -208,18 +199,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -536,24 +515,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="24.85546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="21.42578125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="24.88671875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="25.5546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="21.44140625" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -594,7 +573,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
@@ -635,7 +614,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
@@ -676,7 +655,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -714,47 +693,6 @@
         <v>0.87</v>
       </c>
       <c r="M4" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="13">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13">
-        <v>1240</v>
-      </c>
-      <c r="E5" s="13">
-        <v>1035</v>
-      </c>
-      <c r="F5" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G5" s="13">
-        <v>7</v>
-      </c>
-      <c r="H5" s="13">
-        <v>1400</v>
-      </c>
-      <c r="I5" s="13">
-        <v>980</v>
-      </c>
-      <c r="J5" s="13">
-        <v>12</v>
-      </c>
-      <c r="K5" s="14">
-        <v>1E-10</v>
-      </c>
-      <c r="L5" s="15">
-        <v>0.87</v>
-      </c>
-      <c r="M5" s="15">
         <v>1</v>
       </c>
     </row>

--- a/data/BenchmarkDatabaseCost.xlsx
+++ b/data/BenchmarkDatabaseCost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520BA14F-22C8-4326-93A7-3E7C1D6F5735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3898434F-7DE7-4EE8-8BC9-0F2DF6AAFC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,47 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Material</t>
   </si>
   <si>
-    <t>class</t>
-  </si>
-  <si>
-    <t>class_id</t>
-  </si>
-  <si>
-    <t>Ultimate Strength (MPa)</t>
-  </si>
-  <si>
-    <t>Yield Stress (Mpa)</t>
-  </si>
-  <si>
-    <t>Density (g/cc)</t>
-  </si>
-  <si>
-    <t>Cost ($/lb)</t>
-  </si>
-  <si>
-    <t>Melting Temperature (°C)</t>
-  </si>
-  <si>
-    <t>Max Use Temperature (°C)</t>
-  </si>
-  <si>
-    <t>Elongation to Failure (%)</t>
-  </si>
-  <si>
-    <t>Elastic Modulus (GPa)</t>
-  </si>
-  <si>
-    <t>Ni</t>
-  </si>
-  <si>
-    <t>Criticality Index</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -76,13 +40,25 @@
   </si>
   <si>
     <t>Cost</t>
+  </si>
+  <si>
+    <t>Density</t>
+  </si>
+  <si>
+    <t>Elastic Modulus</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -103,6 +79,39 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -138,16 +147,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -155,50 +164,64 @@
       <left style="hair">
         <color auto="1"/>
       </left>
-      <right style="hair">
+      <right/>
+      <top style="hair">
         <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -515,185 +538,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="24.88671875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="21.44140625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="21.44140625" customWidth="1"/>
-    <col min="12" max="12" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B2" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B5" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="C5" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
-        <v>985</v>
-      </c>
-      <c r="E2" s="6">
-        <v>860</v>
-      </c>
-      <c r="F2" s="10">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="G2" s="6">
-        <v>11</v>
-      </c>
-      <c r="H2" s="6">
-        <v>1330</v>
-      </c>
-      <c r="I2" s="6">
-        <v>870</v>
-      </c>
-      <c r="J2" s="6">
-        <v>7</v>
-      </c>
-      <c r="K2" s="10">
-        <v>2.0000000000000001E-10</v>
-      </c>
-      <c r="L2" s="9">
-        <v>0.87</v>
-      </c>
-      <c r="M2" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>768</v>
-      </c>
-      <c r="E3" s="4">
-        <v>633</v>
-      </c>
-      <c r="F3" s="11">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="G3" s="4">
-        <v>7</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1298</v>
-      </c>
-      <c r="I3" s="4">
-        <v>980</v>
-      </c>
-      <c r="J3" s="4">
-        <v>5</v>
-      </c>
-      <c r="K3" s="11">
-        <v>6E-10</v>
-      </c>
-      <c r="L3" s="8">
-        <v>1</v>
-      </c>
-      <c r="M3" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1240</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1035</v>
-      </c>
-      <c r="F4" s="11">
-        <v>1E-3</v>
-      </c>
-      <c r="G4" s="4">
-        <v>7</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1400</v>
-      </c>
-      <c r="I4" s="4">
-        <v>980</v>
-      </c>
-      <c r="J4" s="4">
-        <v>12</v>
-      </c>
-      <c r="K4" s="11">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="L4" s="8">
-        <v>0.87</v>
-      </c>
-      <c r="M4" s="8">
-        <v>1</v>
+      <c r="B6" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1.4</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/BenchmarkDatabaseCost.xlsx
+++ b/data/BenchmarkDatabaseCost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3898434F-7DE7-4EE8-8BC9-0F2DF6AAFC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4F45C4-67D0-467A-81C2-EF97BB7FE277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Material</t>
   </si>
@@ -46,19 +46,13 @@
   </si>
   <si>
     <t>Elastic Modulus</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -99,20 +93,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="5"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="8" tint="0.39997558519241921"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -177,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -217,12 +197,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -538,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
@@ -602,34 +576,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="C5" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="D5" s="10">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C6" s="9">
-        <v>1.4</v>
-      </c>
-      <c r="D6" s="10">
-        <v>1.3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/BenchmarkDatabaseCost.xlsx
+++ b/data/BenchmarkDatabaseCost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krishnan Suresh\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4F45C4-67D0-467A-81C2-EF97BB7FE277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F636263E-7A00-4AB3-98C8-3AA059DD5CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
@@ -513,14 +513,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,7 +534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
@@ -548,7 +548,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
@@ -562,7 +562,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
